--- a/market-radar-settings-reference.xlsx
+++ b/market-radar-settings-reference.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -558,18 +558,18 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Only tried once every Overpass mirror has failed</t>
+          <t>Only tried once every Overpass mirror has failed (or reported a runtime error)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>GOOGLE_PLACES_API_KEY -- Cloudflare Worker Secret, NOT this sheet</t>
+          <t>GEOAPIFY_API_KEY -- Cloudflare Worker Secret, NOT this sheet</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Free, 3,000 credits/day, no card at myprojects.geoapify.com. NEVER paste the real key into this file -- Settings &gt; Variables and Secrets on the Worker only.</t>
+          <t>Free, 3,000 credits/day, no card at myprojects.geoapify.com. NEVER paste the real key into this file -- Settings &gt; Variables and Secrets on the Worker only. THE SECRET NAME MUST BE EXACTLY GEOAPIFY_API_KEY. CORRECTED 2026-09-20: this row used to say GOOGLE_PLACES_API_KEY (copy-paste error) -- see the 'How to use this' tab.</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
@@ -1506,7 +1505,6 @@
       </c>
       <c r="E58" s="3" t="inlineStr"/>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
@@ -1636,7 +1634,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
@@ -1782,6 +1779,155 @@
       <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Large private employers deliberately excluded — no reliable OSM tag exists for this; use the vacancy-style manual notepad if it matters for a specific spot</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GEOAPIFY BACKSTOP &amp; DIAGNOSTICS -- added 2026-09-20 (v1.4.0)</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Geoapify max places per backstop call</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>GEOAPIFY_RESULT_LIMIT, market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>500 is Geoapify's documented maximum and applies to ALL categories combined, returned nearest-first; if the cap is hit the page warns the count may be an undercount (big drive catchments). Billing appears to be about 1 credit per 20 places RETURNED (inferred from Geoapify's own sample repo: 60,000 places/day on the 3,000-credit free budget; the Places pricing section itself could not be read), so a full answer could cost ~25 credits. Lower this to cap spend per backstop call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Backstop fire-drill switch</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Off (variable not set)</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>FORCE_OVERPASS_FAIL -- a VARIABLE (Type: Text) on the Worker (Settings &gt; Variables and Secrets), not a secret</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Set to 1 to skip Overpass AND its cache, forcing the Geoapify backstop. Run one analysis: the page should say 'via Geoapify backstop'. Then DELETE the variable. Any value other than 1 does nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Overpass soft-failure handling</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>On, always (not adjustable)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>SOFT-FAILURE CHECK inside fetchOverpassPOIs, market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Overpass reports timeouts and out-of-memory as HTTP 200 plus a 'remark' field. A remark containing 'runtime error' (or any remark with zero results) is now treated as a failed mirror: skipped and never cached. A genuine empty answer (no remark) is still accepted as a real '0 competitors'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Worker version (shown on the page)</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>1.4.0</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>WORKER_VERSION, market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>The page prints 'Worker v1.4.0' under Competitors. If it says 'Worker version unknown -- older than v1.4.0', the OLD Worker is still deployed. Keep in step with MARKET_RADAR_VERSION_HISTORY.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Client version (browser console)</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>1.4.0</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>CLIENT_VERSION, market-radar.js</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Press F12 on the page and look for '[Market Radar] script build' in the console. The HTML loads market-radar.js?v=2 so browsers fetch the new file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Geoapify free-plan licence (check before charging customers)</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Free plan listed as 'Limited Commercial Use'; paid plans as 'Commercial Use'</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>External: geoapify.com/pricing -- checked 2026-09-20, not a code setting</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Read Geoapify's terms before selling a product that depends on this backstop. First paid tier listed: 'API 10', 10,000 credits/day, USD 59/month. Geoapify's Places docs say results may be cached/stored with no limits, so the 24h cache is fine.</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1839,6 +1985,13 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-20 CORRECTION (v1.4.0): on the settings tab, row 5 (Geoapify backstop key) used to name the WRONG secret -- GOOGLE_PLACES_API_KEY -- instead of GEOAPIFY_API_KEY. If you created a Worker secret from that name: (1) delete it, (2) create a secret named exactly GEOAPIFY_API_KEY, and (3) rotate the Geoapify key at myprojects.geoapify.com, because under the wrong name the key was sent to Google's servers on each analysis (where Google rejects it). Also added: the 'GEOAPIFY BACKSTOP &amp; DIAGNOSTICS' section at the bottom of the settings tab.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/market-radar-settings-reference.xlsx
+++ b/market-radar-settings-reference.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Only tried once every Overpass mirror has failed (or reported a runtime error)</t>
+          <t>Only tried once every Overpass mirror has failed</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Free, 3,000 credits/day, no card at myprojects.geoapify.com. NEVER paste the real key into this file -- Settings &gt; Variables and Secrets on the Worker only. THE SECRET NAME MUST BE EXACTLY GEOAPIFY_API_KEY. CORRECTED 2026-09-20: this row used to say GOOGLE_PLACES_API_KEY (copy-paste error) -- see the 'How to use this' tab.</t>
+          <t>Free, 3,000 credits/day, no card at myprojects.geoapify.com. NEVER paste the real key into this file -- Settings &gt; Variables and Secrets on the Worker only. The secret's NAME must match exactly (GEOAPIFY_API_KEY): a misspelled name such as geo_api_key silently disables the backstop. This row wrongly listed GOOGLE_PLACES_API_KEY until 2026-09-20.</t>
         </is>
       </c>
     </row>
@@ -599,23 +599,23 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>data.gov.my (population &amp; income)</t>
+          <t>data.gov.my / OpenDOSM (population &amp; income)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>No key needed</t>
+          <t>No key needed. Two endpoints: OpenDOSM API (population) and Data Catalogue API (income)</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>DATA_GOV_MY_ENDPOINT</t>
+          <t>OPENDOSM_ENDPOINT + DATA_GOV_MY_ENDPOINT, market-radar-proxy-worker.js</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Free, but only 4-10 requests/minute total, shared across every visitor to every tool that calls it.</t>
+          <t>Free. 4 requests/minute PER API without a token; OpenDOSM and Data Catalogue are counted separately (developer.data.gov.my/rate-limit, checked 2026-09-20). Population showed "Not available" until 2026-09-20 because it was requested from the wrong endpoint -- see the DOSM section at the bottom.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Same rule: never paste the real key here.</t>
+          <t>Same rule: never paste the real key here. If the read fails with "User location is not supported", Google is blocking the Cloudflare region the Worker happened to run in -- see the NARRATION FALLBACK section at the bottom.</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>NOT free past 1,000 calls/month -- see the cost row directly below before turning this on.</t>
+          <t>NOT free past 1,000 calls/month -- see the cost row directly below before turning this on. Needs a Google Cloud project with billing enabled. The free alternative is the on-site read on the page (see the ON-SITE READ section at the bottom).</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BUSINESS CATEGORIES -- the OSM tags Overpass searches for, one dropdown option each</t>
+          <t>BUSINESS CATEGORIES -- the OSM tags Overpass searches for, one checkbox each (tick up to 4)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -1015,7 +1015,7 @@
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>mr-weight-lowCompetition (page default)</t>
+          <t>SCORE_WEIGHTS_DEFAULT.lowCompetition, market-radar.js (fills the mr-weight-lowCompetition box on page load; the HTML value= is only a fallback)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>mr-weight-population (page default)</t>
+          <t>SCORE_WEIGHTS_DEFAULT.population, market-radar.js (fills the mr-weight-population box on page load; the HTML value= is only a fallback)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>mr-weight-income (page default)</t>
+          <t>SCORE_WEIGHTS_DEFAULT.income, market-radar.js (fills the mr-weight-income box on page load; the HTML value= is only a fallback)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>mr-weight-diversity (page default)</t>
+          <t>SCORE_WEIGHTS_DEFAULT.diversity, market-radar.js (fills the mr-weight-diversity box on page load; the HTML value= is only a fallback)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>mr-weight-momentum (page default)</t>
+          <t>SCORE_WEIGHTS_DEFAULT.momentum, market-radar.js (fills the mr-weight-momentum box on page load; the HTML value= is only a fallback)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1104,12 +1104,12 @@
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>mr-weight-competitorStrength (page default)</t>
+          <t>SCORE_WEIGHTS_DEFAULT.competitorStrength, market-radar.js (fills the mr-weight-competitorStrength box on page load; the HTML value= is only a fallback)</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>NEW 2026-09-16. Google ratings, or your own on-site read. Off by default on purpose -- raise it only if you want it to count.</t>
+          <t>Page default stays 0. CHANGED 2026-09-20: picking an on-site read on the page now sets this to 0.10 automatically (taken from Low competition) so the read visibly counts; clearing the read restores it. Google ratings feed the same weight only if GOOGLE_PLACES_API_KEY is configured.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>12 competitors or more scores lowCompetition at 0.</t>
+          <t>12 competitors or more scores lowCompetition at 0 -- PER BUSINESS TYPE. With several types ticked the threshold is 12 x the number ticked (assumption added 2026-09-20).</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>District names must exactly match one of DOSM's 160 official district names -- confirm at data.gov.my/data-catalogue/population_district before adding a new town.</t>
+          <t>District names must exactly match one of DOSM's 160 official district names -- confirm at open.dosm.gov.my/data-catalogue/population_district before adding a new town.</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>fetchWholesaleRetailTrend(), market-radar-proxy-worker.js</t>
+          <t>fetchWholesaleRetailTrends(), market-radar-proxy-worker.js</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Not on the filterable OpenAPI (confirmed) — this is the actual downloadable CSV DOSM publishes, CC BY 4.0</t>
+          <t>Not on the filterable OpenAPI (confirmed) — this is the actual downloadable CSV DOSM publishes, CC BY 4.0 One download now serves every ticked type (2026-09-20).</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GEOAPIFY BACKSTOP &amp; DIAGNOSTICS -- added 2026-09-20 (v1.4.0)</t>
+          <t>CATCHMENT MODES -- 5-minute walk and drive added 2026-09-20 (the wizard and the page dropdown both read this list)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n"/>
@@ -1796,138 +1796,522 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Geoapify max places per backstop call</t>
+          <t>5-minute walk</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>foot-walking, 300 s; plain-circle fallback radius 400 m</t>
         </is>
       </c>
       <c r="C78" s="4" t="n"/>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>GEOAPIFY_RESULT_LIMIT, market-radar-proxy-worker.js</t>
+          <t>CATCHMENT_MODES.walk5, market-radar.js</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>500 is Geoapify's documented maximum and applies to ALL categories combined, returned nearest-first; if the cap is hit the page warns the count may be an undercount (big drive catchments). Billing appears to be about 1 credit per 20 places RETURNED (inferred from Geoapify's own sample repo: 60,000 places/day on the 3,000-credit free budget; the Places pricing section itself could not be read), so a full answer could cost ~25 credits. Lower this to cap spend per backstop call.</t>
+          <t>NEW 2026-09-20.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Backstop fire-drill switch</t>
+          <t>10-minute walk</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Off (variable not set)</t>
+          <t>foot-walking, 600 s; fallback radius 800 m</t>
         </is>
       </c>
       <c r="C79" s="4" t="n"/>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>FORCE_OVERPASS_FAIL -- a VARIABLE (Type: Text) on the Worker (Settings &gt; Variables and Secrets), not a secret</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>Set to 1 to skip Overpass AND its cache, forcing the Geoapify backstop. Run one analysis: the page should say 'via Geoapify backstop'. Then DELETE the variable. Any value other than 1 does nothing.</t>
-        </is>
-      </c>
+          <t>CATCHMENT_MODES.walk10, market-radar.js</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Overpass soft-failure handling</t>
+          <t>15-minute walk</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>On, always (not adjustable)</t>
+          <t>foot-walking, 900 s; fallback radius 1,200 m</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>SOFT-FAILURE CHECK inside fetchOverpassPOIs, market-radar-proxy-worker.js</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>Overpass reports timeouts and out-of-memory as HTTP 200 plus a 'remark' field. A remark containing 'runtime error' (or any remark with zero results) is now treated as a failed mirror: skipped and never cached. A genuine empty answer (no remark) is still accepted as a real '0 competitors'.</t>
-        </is>
-      </c>
+          <t>CATCHMENT_MODES.walk15, market-radar.js</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Worker version (shown on the page)</t>
+          <t>5-minute drive</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>driving-car, 300 s; fallback radius 2,500 m</t>
         </is>
       </c>
       <c r="C81" s="4" t="n"/>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>WORKER_VERSION, market-radar-proxy-worker.js</t>
+          <t>CATCHMENT_MODES.drive5, market-radar.js</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>The page prints 'Worker v1.4.0' under Competitors. If it says 'Worker version unknown -- older than v1.4.0', the OLD Worker is still deployed. Keep in step with MARKET_RADAR_VERSION_HISTORY.md.</t>
+          <t>NEW 2026-09-20.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Client version (browser console)</t>
+          <t>10-minute drive</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>1.4.0</t>
+          <t>driving-car, 600 s; fallback radius 5,000 m</t>
         </is>
       </c>
       <c r="C82" s="4" t="n"/>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>CLIENT_VERSION, market-radar.js</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>Press F12 on the page and look for '[Market Radar] script build' in the console. The HTML loads market-radar.js?v=2 so browsers fetch the new file.</t>
-        </is>
-      </c>
+          <t>CATCHMENT_MODES.drive10, market-radar.js</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Geoapify free-plan licence (check before charging customers)</t>
+          <t>15-minute drive</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Free plan listed as 'Limited Commercial Use'; paid plans as 'Commercial Use'</t>
+          <t>driving-car, 900 s; fallback radius 8,000 m</t>
         </is>
       </c>
       <c r="C83" s="4" t="n"/>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>External: geoapify.com/pricing -- checked 2026-09-20, not a code setting</t>
+          <t>CATCHMENT_MODES.drive15, market-radar.js</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Read Geoapify's terms before selling a product that depends on this backstop. First paid tier listed: 'API 10', 10,000 credits/day, USD 59/month. Geoapify's Places docs say results may be cached/stored with no limits, so the 24h cache is fine.</t>
+          <t>Fallback radius = the plain dashed circle drawn if the real travel-time shape cannot be fetched. The Worker searches 1.3x that distance, then trims to the real shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>BUSINESS-TYPE PICKER -- tick up to 4 (checkboxes replaced the dropdown 2026-09-20)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Most business types ticked at once</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>MAX_CATEGORIES, market-radar.js</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Change the number and the page enforces the new cap by itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Ticked when the page opens</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Cafe / kopitiam</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>DEFAULT_CATEGORIES, market-radar.js</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Saturation with several types ticked</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>SATURATION_COUNT x number of types ticked (e.g. 3 types -&gt; 36)</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>computeOpportunityScore(), market-radar.js</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMPTION made 2026-09-20: 12 per type, so ticking four food types is not scored as four times as crowded. Tune it with the SATURATION_COUNT row above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Characters allowed in a custom OSM key/value</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>letters, numbers, _ : - (max 40)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOM_TAG_PATTERN (market-radar.js) and TAG_TOKEN (Worker)</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Enforced in both places; anything else is rejected before it can reach an Overpass query. Custom counts as one of the 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>ON-SITE READ -&gt; SCORE (changed 2026-09-20)</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Weight applied automatically when you pick an on-site read</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>0.10, taken from Low competition</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>ON_SITE_AUTO_WEIGHT, market-radar.js</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Before this, picking a read did nothing unless Competitor strength was already raised above 0. Clearing the read restores both weights; editing any weight by hand switches the automation off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>NARRATION FALLBACK -- Gemini first, Cloudflare Workers AI as backstop (added 2026-09-20)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Workers AI binding</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Optional. A BINDING (not a secret) named exactly AI</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare dashboard: Worker &gt; Settings &gt; Bindings &gt; Add &gt; Workers AI</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Fixes Gemini's "User location is not supported for the API use": Cloudflare ran the Worker in a region Google blocks (Hong Kong is the one reported on Cloudflare's community forum), and that changes request to request. Free: 10,000 neurons/day (Cloudflare pricing page, 2026-09-17), about 10 per read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Workers AI model</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>@cf/meta/llama-3.1-8b-instruct-fp8-fast</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>WORKERS_AI_MODEL, market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Cloudflare retires models now and then (18 older ones on 30 May 2026). If reads stop, pick a current text model from developers.cloudflare.com/workers-ai/platform/pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>DOSM POPULATION &amp; INCOME -- which endpoint serves which dataset (fixed 2026-09-20)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Population dataset</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>population_district via the OpenDOSM API: https://api.data.gov.my/opendosm</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>OPENDOSM_ENDPOINT + fetchPopulation(), market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Root cause of "Not available": the Data Catalogue endpoint returns an empty list [] for this dataset (checked 2026-09-20 -- even the dataset page's own sample query). Figure is in THOUSANDS; the both/overall/overall row is the district total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Income dataset</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>hh_income_district via the Data Catalogue API: https://api.data.gov.my/data-catalogue</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>DATA_GOV_MY_ENDPOINT + fetchIncome(), market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Each dataset also tries the other endpoint as a fallback, in case DOSM moves it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Rate limit</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>4 requests/minute per API, no token</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>developer.data.gov.my/rate-limit</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Each analysis makes one call to each API. A rate-limited call now says so on the card instead of a bare "Not available".</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Demographics cache</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>7 days, successes only, key demographics-v2</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>fetchDemographics(), market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>The old code cached a FAILED lookup for a week. Cloudflare only guarantees its Cache API on custom domains, so nothing depends on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>10-second check you can do yourself</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Paste in a browser tab: https://api.data.gov.my/opendosm?id=population_district&amp;ifilter=Miri@district&amp;limit=3</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>n/a (external)</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Should show JSON rows with "district": "Miri". If it shows [], try the partial-match version: ...&amp;icontains=miri@district&amp;limit=3 -- the district spelling is then the issue, not the code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>WORKER SAFETY LIMITS (added 2026-09-20 -- the Worker is public, so it checks what it is sent)</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Largest search radius accepted</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>12,000 m</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>MAX_RADIUS_M, market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Your longest catchment (15-minute drive) needs 10,400 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Most OSM tag pairs accepted per request</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>40 business + 30 institution</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>MAX_CATEGORY_TAG_PAIRS / MAX_ANCHOR_TAG_PAIRS, market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>The page currently sends about 34 in total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Worker version shown on the page</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>1.5.0</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>WORKER_VERSION, market-radar-proxy-worker.js</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Appears under "Competitors in catchment". Bump it on every deploy so you can tell at a glance which version is live.</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2372,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-20 CORRECTION (v1.4.0): on the settings tab, row 5 (Geoapify backstop key) used to name the WRONG secret -- GOOGLE_PLACES_API_KEY -- instead of GEOAPIFY_API_KEY. If you created a Worker secret from that name: (1) delete it, (2) create a secret named exactly GEOAPIFY_API_KEY, and (3) rotate the Geoapify key at myprojects.geoapify.com, because under the wrong name the key was sent to Google's servers on each analysis (where Google rejects it). Also added: the 'GEOAPIFY BACKSTOP &amp; DIAGNOSTICS' section at the bottom of the settings tab.</t>
+          <t>2026-09-20 update (v1.5.0): added the catchment-mode, business-type-picker, on-site-read, narration-fallback, DOSM-endpoint and Worker-safety-limit sections at the bottom of the settings sheet, and corrected row 5 (the Geoapify secret is GEOAPIFY_API_KEY -- this sheet used to say GOOGLE_PLACES_API_KEY). The full story of each change is in MARKET_RADAR_SETUP_AND_GLOSSARY.md; the architecture is in MARKET_RADAR_HANDOFF.md.</t>
         </is>
       </c>
     </row>
